--- a/Ecuatia de Stare/izocora.xlsx
+++ b/Ecuatia de Stare/izocora.xlsx
@@ -271,7 +271,7 @@
   <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="26.64"/>
   </cols>
   <sheetData>
@@ -305,18 +305,10 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1"/>
       <c r="E2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
